--- a/docs/2e/bases-de-donnees/meteo.xlsx
+++ b/docs/2e/bases-de-donnees/meteo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caro\Documents\Projets\t-doc\informatique\docs\2e\bases-de-donnees\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DA76F1-3338-41CD-9252-6038925528E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75007838-24D0-4D3C-9003-CC68D9275D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{E8FB6D54-8182-47F2-A6BF-6FB10867FC41}"/>
   </bookViews>
@@ -92,13 +92,13 @@
     <t>Dec</t>
   </si>
   <si>
-    <t>Geneve</t>
-  </si>
-  <si>
     <t>Températures minimales moyennes (en °C)</t>
   </si>
   <si>
     <t>Températures maximales moyennes (en °C)</t>
+  </si>
+  <si>
+    <t>Genève</t>
   </si>
 </sst>
 </file>
@@ -142,16 +142,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,29 +488,28 @@
   <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="4"/>
-    <col min="2" max="16384" width="10.90625" style="3"/>
+    <col min="1" max="1" width="10.90625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4"/>
+      <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,267 +548,267 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>-4.8</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>-4.5</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>-1.4</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>1.7</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>6.1</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>10.199999999999999</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>12.1</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3">
         <v>12.1</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3">
         <v>5.0999999999999996</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3">
         <v>0.1</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3">
         <v>-3.3</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
         <v>-2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>-1.7</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>4.7</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>12.7</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>14.7</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4">
         <v>14.5</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4">
         <v>10.7</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4">
         <v>6.8</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4">
         <v>1.8</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4">
         <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>-1.9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>0.7</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>3.9</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>8.4</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>12.4</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>14.4</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5">
         <v>14.5</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5">
         <v>10.9</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5">
         <v>7</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5">
         <v>-0.9</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>-3</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>-3</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>11</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6">
         <v>13</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6">
         <v>-2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>0.5</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>0.4</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>2.8</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>5.9</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>9.9</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>14.2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>16.7</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7">
         <v>16.899999999999999</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7">
         <v>13.5</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7">
         <v>9.9</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7">
         <v>5</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7">
         <v>1.7</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>-1.7</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>4.2</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>8.1</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8">
         <v>12.4</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>14.7</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8">
         <v>14.9</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8">
         <v>11.5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8">
         <v>7.7</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8">
         <v>2.8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8">
         <v>-1.4</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
     </row>
     <row r="11" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
@@ -851,267 +849,267 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>2.7</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>3.7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12">
         <v>12.1</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12">
         <v>15.7</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12">
         <v>19.7</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12">
         <v>21.4</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12">
         <v>21.1</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12">
         <v>17.2</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12">
         <v>13.6</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12">
         <v>7.4</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12">
         <v>3.6</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>5.2</v>
+      </c>
+      <c r="D13">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E13">
+        <v>14.1</v>
+      </c>
+      <c r="F13">
+        <v>17.5</v>
+      </c>
+      <c r="G13">
+        <v>21.6</v>
+      </c>
+      <c r="H13">
+        <v>23.4</v>
+      </c>
+      <c r="I13">
+        <v>23</v>
+      </c>
+      <c r="J13">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="K13">
+        <v>15.3</v>
+      </c>
+      <c r="L13">
+        <v>8.9</v>
+      </c>
+      <c r="M13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>4.2</v>
+      </c>
+      <c r="C14">
+        <v>5.3</v>
+      </c>
+      <c r="D14">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="G14">
+        <v>21.5</v>
+      </c>
+      <c r="H14">
+        <v>23.1</v>
+      </c>
+      <c r="I14">
+        <v>22.8</v>
+      </c>
+      <c r="J14">
+        <v>18.7</v>
+      </c>
+      <c r="K14">
+        <v>14.6</v>
+      </c>
+      <c r="L14">
+        <v>8.6</v>
+      </c>
+      <c r="M14">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>17</v>
+      </c>
+      <c r="G15">
+        <v>21</v>
+      </c>
+      <c r="H15">
+        <v>23</v>
+      </c>
+      <c r="I15">
+        <v>23</v>
+      </c>
+      <c r="J15">
         <v>18</v>
       </c>
-      <c r="B13" s="3">
-        <v>4</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="K15">
+        <v>13</v>
+      </c>
+      <c r="L15">
+        <v>7</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>5.8</v>
+      </c>
+      <c r="D16">
+        <v>9.6</v>
+      </c>
+      <c r="E16">
+        <v>13.5</v>
+      </c>
+      <c r="F16">
+        <v>17</v>
+      </c>
+      <c r="G16">
+        <v>21.1</v>
+      </c>
+      <c r="H16">
+        <v>23</v>
+      </c>
+      <c r="I16">
+        <v>22.8</v>
+      </c>
+      <c r="J16">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="K16">
+        <v>15.4</v>
+      </c>
+      <c r="L16">
+        <v>9.5</v>
+      </c>
+      <c r="M16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C17">
         <v>5.2</v>
       </c>
-      <c r="D13" s="3">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="E13" s="3">
-        <v>14.1</v>
-      </c>
-      <c r="F13" s="3">
-        <v>17.5</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="D17">
+        <v>9.5</v>
+      </c>
+      <c r="E17">
+        <v>13.2</v>
+      </c>
+      <c r="F17">
+        <v>17.2</v>
+      </c>
+      <c r="G17">
         <v>21.6</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H17">
         <v>23.4</v>
       </c>
-      <c r="I13" s="3">
-        <v>23</v>
-      </c>
-      <c r="J13" s="3">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="K13" s="3">
-        <v>15.3</v>
-      </c>
-      <c r="L13" s="3">
-        <v>8.9</v>
-      </c>
-      <c r="M13" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="C14" s="3">
-        <v>5.3</v>
-      </c>
-      <c r="D14" s="3">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="I17">
+        <v>22.7</v>
+      </c>
+      <c r="J17">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="K17">
         <v>14</v>
       </c>
-      <c r="F14" s="3">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="G14" s="3">
-        <v>21.5</v>
-      </c>
-      <c r="H14" s="3">
-        <v>23.1</v>
-      </c>
-      <c r="I14" s="3">
-        <v>22.8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>18.7</v>
-      </c>
-      <c r="K14" s="3">
-        <v>14.6</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L17">
         <v>8.6</v>
       </c>
-      <c r="M14" s="3">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="3">
-        <v>3</v>
-      </c>
-      <c r="C15" s="3">
-        <v>5</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="M17">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="3">
-        <v>13</v>
-      </c>
-      <c r="F15" s="3">
-        <v>17</v>
-      </c>
-      <c r="G15" s="3">
-        <v>21</v>
-      </c>
-      <c r="H15" s="3">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3">
-        <v>23</v>
-      </c>
-      <c r="J15" s="3">
-        <v>18</v>
-      </c>
-      <c r="K15" s="3">
-        <v>13</v>
-      </c>
-      <c r="L15" s="3">
-        <v>7</v>
-      </c>
-      <c r="M15" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="3">
-        <v>5</v>
-      </c>
-      <c r="C16" s="3">
-        <v>5.8</v>
-      </c>
-      <c r="D16" s="3">
-        <v>9.6</v>
-      </c>
-      <c r="E16" s="3">
-        <v>13.5</v>
-      </c>
-      <c r="F16" s="3">
-        <v>17</v>
-      </c>
-      <c r="G16" s="3">
-        <v>21.1</v>
-      </c>
-      <c r="H16" s="3">
-        <v>23</v>
-      </c>
-      <c r="I16" s="3">
-        <v>22.8</v>
-      </c>
-      <c r="J16" s="3">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="K16" s="3">
-        <v>15.4</v>
-      </c>
-      <c r="L16" s="3">
-        <v>9.5</v>
-      </c>
-      <c r="M16" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="3">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>9.5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>13.2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>17.2</v>
-      </c>
-      <c r="G17" s="3">
-        <v>21.6</v>
-      </c>
-      <c r="H17" s="3">
-        <v>23.4</v>
-      </c>
-      <c r="I17" s="3">
-        <v>22.7</v>
-      </c>
-      <c r="J17" s="3">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="K17" s="3">
-        <v>14</v>
-      </c>
-      <c r="L17" s="3">
-        <v>8.6</v>
-      </c>
-      <c r="M17" s="3">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
@@ -1152,248 +1150,248 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>105</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21">
         <v>99</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21">
         <v>104</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21">
         <v>114</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>161</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>158</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21">
         <v>166</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21">
         <v>152</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21">
         <v>123</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21">
         <v>107</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21">
         <v>119</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21">
         <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
         <v>118</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22">
         <v>106</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22">
         <v>112</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22">
         <v>116</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22">
         <v>147</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>129</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22">
         <v>128</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22">
         <v>119</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22">
         <v>113</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22">
         <v>115</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22">
         <v>132</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22">
         <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>97</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23">
         <v>90</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23">
         <v>104</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23">
         <v>112</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23">
         <v>150</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23">
         <v>149</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <v>152</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23">
         <v>149</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23">
         <v>128</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23">
         <v>106</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23">
         <v>115</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23">
         <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <v>69</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24">
         <v>66</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24">
         <v>61</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24">
         <v>69</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24">
         <v>81</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24">
         <v>106</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24">
         <v>95</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24">
         <v>121</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24">
         <v>80</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24">
         <v>57</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24">
         <v>85</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25">
         <v>112</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25">
         <v>102</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25">
         <v>98</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25">
         <v>96</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25">
         <v>123</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>111</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25">
         <v>123</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25">
         <v>118</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25">
         <v>112</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K25">
         <v>104</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25">
         <v>123</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25">
         <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26">
         <v>71</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26">
         <v>68</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26">
         <v>87</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26">
         <v>150</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26">
         <v>165</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>173</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <v>146</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26">
         <v>173</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26">
         <v>175</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26">
         <v>182</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26">
         <v>188</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26">
         <v>80</v>
       </c>
     </row>
